--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8064516129032258</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4347826086956522</v>
+        <v>0.3873239436619718</v>
       </c>
       <c r="D2">
-        <v>0.7572815533980582</v>
+        <v>0.75</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8529411764705882</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3873239436619718</v>
+        <v>0.3802816901408451</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>0.7927927927927928</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
